--- a/data/trans_camb/P57GLOBAL_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 5,06</t>
+          <t>-8,46; 4,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 15,64</t>
+          <t>3,83; 15,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,52; -4,43</t>
+          <t>-17,12; -4,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 11,51</t>
+          <t>-3,92; 11,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 20,48</t>
+          <t>6,35; 20,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -6,56</t>
+          <t>-19,74; -5,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,73</t>
+          <t>-4,32; 5,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 16,23</t>
+          <t>7,25; 16,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,18; -7,64</t>
+          <t>-16,13; -6,72</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 7,7</t>
+          <t>-11,67; 6,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 23,94</t>
+          <t>5,3; 23,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,43; -6,71</t>
+          <t>-23,82; -6,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 19,13</t>
+          <t>-5,52; 18,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 33,56</t>
+          <t>8,78; 32,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,27; -10,11</t>
+          <t>-28,02; -9,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 8,82</t>
+          <t>-6,15; 8,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 24,59</t>
+          <t>10,32; 24,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,05; -11,48</t>
+          <t>-23,0; -10,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 10,77</t>
+          <t>-3,32; 10,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 19,51</t>
+          <t>6,06; 19,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 6,83</t>
+          <t>-7,54; 6,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 12,04</t>
+          <t>-1,61; 12,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 18,66</t>
+          <t>5,86; 18,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 3,46</t>
+          <t>-10,3; 2,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 8,83</t>
+          <t>-1,09; 9,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 17,3</t>
+          <t>8,02; 17,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,39</t>
+          <t>-6,31; 3,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 17,63</t>
+          <t>-4,84; 17,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 32,29</t>
+          <t>8,91; 33,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 11,37</t>
+          <t>-11,16; 10,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 18,39</t>
+          <t>-2,17; 19,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 29,04</t>
+          <t>8,06; 29,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 5,53</t>
+          <t>-14,09; 4,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 13,65</t>
+          <t>-1,34; 14,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 27,2</t>
+          <t>11,72; 27,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 3,83</t>
+          <t>-9,09; 4,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -1,55</t>
+          <t>-12,01; -0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 16,41</t>
+          <t>7,06; 16,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-58,11; -8,26</t>
+          <t>-59,84; -7,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 10,02</t>
+          <t>-7,55; 9,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 24,71</t>
+          <t>8,46; 24,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 5,38</t>
+          <t>-12,87; 6,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -0,08</t>
+          <t>-8,77; -0,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 17,15</t>
+          <t>8,39; 16,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-51,24; -6,01</t>
+          <t>-54,86; -6,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -2,21</t>
+          <t>-15,4; -1,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 22,82</t>
+          <t>8,94; 23,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,71; -11,14</t>
+          <t>-78,78; -10,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 14,92</t>
+          <t>-9,83; 15,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 38,11</t>
+          <t>11,42; 38,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 8,11</t>
+          <t>-16,77; 9,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,04; -0,18</t>
+          <t>-11,49; -0,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,28; 24,08</t>
+          <t>11,08; 23,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,49; -8,15</t>
+          <t>-74,45; -8,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,15</t>
+          <t>-6,11; 1,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,86</t>
+          <t>5,72; 12,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -3,3</t>
+          <t>-11,91; -3,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,86</t>
+          <t>0,88; 10,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,22</t>
+          <t>7,16; 15,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,76; -6,58</t>
+          <t>-15,45; -6,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,12</t>
+          <t>-2,09; 3,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 12,97</t>
+          <t>7,59; 12,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -5,76</t>
+          <t>-12,06; -6,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,61</t>
+          <t>-8,31; 2,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 18,09</t>
+          <t>7,59; 17,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -4,7</t>
+          <t>-15,88; -4,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 13,75</t>
+          <t>1,14; 14,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,51; 21,18</t>
+          <t>9,33; 21,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -9,21</t>
+          <t>-20,42; -9,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,36</t>
+          <t>-2,8; 4,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,05; 18,12</t>
+          <t>10,13; 17,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -8,05</t>
+          <t>-16,1; -8,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 7,1</t>
+          <t>-5,57; 6,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 17,24</t>
+          <t>5,84; 17,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 4,38</t>
+          <t>-9,24; 4,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 2,15</t>
+          <t>-7,45; 2,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 11,39</t>
+          <t>3,94; 12,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -8,19</t>
+          <t>-31,54; -8,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 2,16</t>
+          <t>-5,0; 2,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,6; 12,16</t>
+          <t>5,61; 12,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,56; -5,42</t>
+          <t>-24,9; -5,72</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 10,49</t>
+          <t>-7,33; 9,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,38; 25,76</t>
+          <t>7,75; 25,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 6,31</t>
+          <t>-12,18; 6,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 2,85</t>
+          <t>-9,07; 2,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,01; 14,75</t>
+          <t>4,85; 15,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -10,4</t>
+          <t>-39,57; -11,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 2,9</t>
+          <t>-6,31; 3,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,12; 16,33</t>
+          <t>7,16; 16,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -7,26</t>
+          <t>-32,21; -7,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 8,93</t>
+          <t>-7,04; 8,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,15; 26,62</t>
+          <t>11,56; 26,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,43; -2,69</t>
+          <t>-26,93; -2,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,63</t>
+          <t>-0,65; 6,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,9</t>
+          <t>10,78; 17,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -1,2</t>
+          <t>-10,05; -1,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,66</t>
+          <t>-0,73; 6,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>11,73; 18,16</t>
+          <t>12,02; 18,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -3,92</t>
+          <t>-13,59; -4,3</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 15,52</t>
+          <t>-10,85; 16,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17,37; 47,71</t>
+          <t>18,64; 47,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,71; -4,54</t>
+          <t>-42,37; -3,06</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 9,69</t>
+          <t>-0,9; 9,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15,03; 26,27</t>
+          <t>14,94; 25,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -1,76</t>
+          <t>-14,04; -2,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,51</t>
+          <t>-1,1; 9,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16,81; 27,42</t>
+          <t>17,17; 27,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -5,99</t>
+          <t>-19,39; -6,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,92</t>
+          <t>-3,58; 0,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,97</t>
+          <t>9,52; 13,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-25,6; -6,55</t>
+          <t>-27,76; -6,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,25</t>
+          <t>0,94; 5,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,51</t>
+          <t>10,52; 14,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -7,12</t>
+          <t>-14,87; -7,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,52</t>
+          <t>-0,75; 2,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,57; 13,46</t>
+          <t>10,45; 13,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-20,31; -7,95</t>
+          <t>-19,47; -7,85</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 1,34</t>
+          <t>-5,04; 1,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,23; 20,25</t>
+          <t>13,29; 19,59</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,59; -9,39</t>
+          <t>-39,97; -9,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,33</t>
+          <t>1,3; 7,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,63; 20,42</t>
+          <t>14,25; 20,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -10,0</t>
+          <t>-20,56; -10,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,57</t>
+          <t>-1,03; 3,2</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,18</t>
+          <t>14,43; 19,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-28,42; -11,17</t>
+          <t>-27,49; -11,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57GLOBAL_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,68</t>
+          <t>-9,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,07</t>
+          <t>-12,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-11,96</t>
+          <t>-10,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,59</t>
+          <t>-6,97; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 15,73</t>
+          <t>4,51; 16,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -4,52</t>
+          <t>-15,76; -3,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 11,46</t>
+          <t>-4,3; 10,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 20,61</t>
+          <t>6,71; 20,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,74; -5,78</t>
+          <t>-19,27; -5,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,53</t>
+          <t>-4,08; 5,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 16,02</t>
+          <t>7,18; 16,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,13; -6,72</t>
+          <t>-15,32; -6,09</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,49%</t>
+          <t>-13,78%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,52%</t>
+          <t>-18,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,55%</t>
+          <t>-15,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 6,97</t>
+          <t>-9,75; 8,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 23,68</t>
+          <t>6,41; 25,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,82; -6,79</t>
+          <t>-21,88; -4,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 18,52</t>
+          <t>-6,04; 17,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 32,65</t>
+          <t>9,75; 32,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -9,6</t>
+          <t>-27,68; -8,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 8,38</t>
+          <t>-5,78; 8,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 24,45</t>
+          <t>10,13; 25,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,0; -10,39</t>
+          <t>-21,53; -9,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,61</t>
+          <t>-4,5; 10,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 19,74</t>
+          <t>5,61; 19,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 6,56</t>
+          <t>-5,21; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 12,53</t>
+          <t>-1,34; 12,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,85</t>
+          <t>5,63; 19,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 2,96</t>
+          <t>-10,84; 2,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 9,07</t>
+          <t>-0,78; 9,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 17,29</t>
+          <t>7,65; 17,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 3,16</t>
+          <t>-5,99; 3,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,36%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,22%</t>
+          <t>-5,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,89%</t>
+          <t>-1,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 17,18</t>
+          <t>-6,45; 16,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 33,2</t>
+          <t>8,24; 32,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 10,53</t>
+          <t>-7,79; 13,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 19,2</t>
+          <t>-1,87; 19,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 29,71</t>
+          <t>7,84; 29,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 4,5</t>
+          <t>-15,04; 3,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 14,56</t>
+          <t>-1,06; 15,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 27,31</t>
+          <t>11,23; 27,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 4,99</t>
+          <t>-8,62; 6,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-33,67</t>
+          <t>-9,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-5,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-27,64</t>
+          <t>-8,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -0,99</t>
+          <t>-11,87; -1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 16,9</t>
+          <t>7,0; 16,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-59,84; -7,84</t>
+          <t>-15,6; -3,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 9,97</t>
+          <t>-7,74; 10,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 24,92</t>
+          <t>7,88; 25,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 6,28</t>
+          <t>-13,32; 4,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -0,01</t>
+          <t>-8,93; 0,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 16,83</t>
+          <t>9,07; 17,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-54,86; -6,26</t>
+          <t>-13,08; -3,24</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-45,04%</t>
+          <t>-13,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,44%</t>
+          <t>-7,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-37,34%</t>
+          <t>-11,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,4; -1,22</t>
+          <t>-15,44; -1,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 23,6</t>
+          <t>9,06; 23,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -10,66</t>
+          <t>-20,58; -5,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 15,02</t>
+          <t>-10,14; 16,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,42; 38,3</t>
+          <t>10,36; 38,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 9,75</t>
+          <t>-17,56; 7,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -0,02</t>
+          <t>-11,85; 0,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,08; 23,74</t>
+          <t>11,82; 24,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,45; -8,6</t>
+          <t>-17,2; -4,64</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-6,62</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,25</t>
+          <t>-9,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-7,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,43</t>
+          <t>-6,2; 1,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 12,56</t>
+          <t>5,66; 12,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -3,26</t>
+          <t>-10,65; -2,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 10,13</t>
+          <t>0,69; 9,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,39</t>
+          <t>7,18; 15,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,45; -6,63</t>
+          <t>-13,91; -5,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,57</t>
+          <t>-2,34; 3,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,65</t>
+          <t>7,8; 12,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -6,26</t>
+          <t>-10,53; -4,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,46%</t>
+          <t>-9,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,08%</t>
+          <t>-13,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,33%</t>
+          <t>-10,69%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 2,01</t>
+          <t>-8,28; 1,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,45</t>
+          <t>7,63; 17,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,88; -4,34</t>
+          <t>-14,39; -4,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 14,21</t>
+          <t>0,9; 13,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,33; 21,49</t>
+          <t>9,26; 21,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -9,15</t>
+          <t>-18,37; -7,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,95</t>
+          <t>-3,2; 4,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 17,63</t>
+          <t>10,38; 18,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -8,63</t>
+          <t>-14,26; -6,81</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,6</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-17,24</t>
+          <t>-7,34</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-11,8</t>
+          <t>-5,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,58</t>
+          <t>-5,0; 7,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 17,17</t>
+          <t>6,14; 17,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 4,75</t>
+          <t>-8,89; 4,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,08</t>
+          <t>-7,02; 2,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 12,02</t>
+          <t>3,45; 11,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,54; -8,68</t>
+          <t>-11,57; -3,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,36</t>
+          <t>-4,99; 2,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,1</t>
+          <t>5,32; 12,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-24,9; -5,72</t>
+          <t>-9,0; -1,61</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,62%</t>
+          <t>-2,88%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-21,66%</t>
+          <t>-9,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,39%</t>
+          <t>-7,03%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 9,64</t>
+          <t>-6,81; 10,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,75; 25,55</t>
+          <t>8,04; 26,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 6,99</t>
+          <t>-11,93; 6,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 2,72</t>
+          <t>-8,55; 2,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,85; 15,84</t>
+          <t>4,15; 15,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,57; -11,12</t>
+          <t>-14,07; -4,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 3,19</t>
+          <t>-6,31; 3,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,16; 16,34</t>
+          <t>6,74; 16,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -7,66</t>
+          <t>-11,44; -2,04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-14,91</t>
+          <t>-12,03</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>-4,71</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-8,48</t>
+          <t>-6,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 8,87</t>
+          <t>-6,79; 9,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,56; 26,54</t>
+          <t>12,04; 25,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,93; -2,07</t>
+          <t>-23,85; -0,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,76</t>
+          <t>-0,8; 6,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,78; 17,58</t>
+          <t>11,11; 18,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,05; -1,59</t>
+          <t>-9,01; -0,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 6,13</t>
+          <t>-0,59; 5,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>12,02; 18,33</t>
+          <t>11,99; 18,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,59; -4,3</t>
+          <t>-11,03; -2,44</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-19,98%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-8,17%</t>
+          <t>-6,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-12,41%</t>
+          <t>-9,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 16,5</t>
+          <t>-10,82; 16,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18,64; 47,89</t>
+          <t>18,93; 46,53</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -3,06</t>
+          <t>-37,7; -1,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 9,92</t>
+          <t>-1,13; 9,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,94; 25,77</t>
+          <t>15,42; 26,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -2,29</t>
+          <t>-12,48; -1,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,05</t>
+          <t>-0,84; 8,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17,17; 27,51</t>
+          <t>17,04; 27,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,39; -6,4</t>
+          <t>-15,88; -3,66</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,0</t>
+          <t>-6,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-9,84</t>
+          <t>-6,94</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-10,94</t>
+          <t>-6,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,92</t>
+          <t>-3,77; 0,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,52; 13,62</t>
+          <t>9,18; 13,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-27,76; -6,57</t>
+          <t>-8,26; -3,55</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,07</t>
+          <t>1,04; 5,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,5</t>
+          <t>10,56; 14,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -7,17</t>
+          <t>-8,98; -4,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,26</t>
+          <t>-0,74; 2,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,45; 13,41</t>
+          <t>10,5; 13,35</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -7,85</t>
+          <t>-8,26; -5,02</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-17,04%</t>
+          <t>-8,74%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-13,61%</t>
+          <t>-9,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-15,33%</t>
+          <t>-9,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,32</t>
+          <t>-5,26; 1,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,29; 19,59</t>
+          <t>12,87; 19,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,97; -9,39</t>
+          <t>-11,66; -5,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,13</t>
+          <t>1,44; 7,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,25; 20,22</t>
+          <t>14,37; 20,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -10,03</t>
+          <t>-12,23; -6,77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,2</t>
+          <t>-1,02; 3,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,01</t>
+          <t>14,52; 18,83</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,49; -11,06</t>
+          <t>-11,48; -7,09</t>
         </is>
       </c>
     </row>
